--- a/www/ig/fhir/core/StructureDefinition-fr-core-encounter.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="614">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Encounter</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Encounter|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -428,7 +428,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -441,14 +441,14 @@
     <t>Encounter.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -470,6 +470,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0</t>
+  </si>
+  <si>
     <t>Encounter.meta.security</t>
   </si>
   <si>
@@ -492,7 +495,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -516,7 +519,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -559,7 +562,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -635,7 +638,7 @@
     <t>estimatedDischargeDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date|2.2.0}
 </t>
   </si>
   <si>
@@ -745,7 +748,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type|2.2.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -831,7 +834,7 @@
     <t>Encounter.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -946,7 +949,7 @@
     <t>Classification of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -1127,7 +1130,7 @@
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type|2.2.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1151,7 +1154,7 @@
     <t>Broad categorization of the service that is to be provided.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>PV1-10</t>
@@ -1166,7 +1169,7 @@
     <t>Indicates the urgency of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority|3.0.0</t>
   </si>
   <si>
     <t>.priorityCode</t>
@@ -1185,7 +1188,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1213,7 +1216,7 @@
     <t>Encounter.episodeOfCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(EpisodeOfCare)
+    <t xml:space="preserve">Reference(EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1239,7 +1242,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1294,7 +1297,7 @@
     <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1324,7 +1327,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1349,7 +1352,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.2.0)
 </t>
   </si>
   <si>
@@ -1430,7 +1433,7 @@
     <t>Reason why the encounter takes place.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1448,7 +1451,7 @@
     <t>Encounter.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure|Observation|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1|Observation|4.0.1|ImmunizationRecommendation|4.0.1)
 </t>
   </si>
   <si>
@@ -1483,7 +1486,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -1514,7 +1517,7 @@
     <t>The type of diagnosis this condition represents.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnosis-role</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.0.1</t>
   </si>
   <si>
     <t>Encounter.diagnosis.rank</t>
@@ -1536,7 +1539,7 @@
     <t>Encounter.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Account)
+    <t xml:space="preserve">Reference(Account|4.0.1)
 </t>
   </si>
   <si>
@@ -1627,7 +1630,7 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1652,7 +1655,7 @@
     <t>From where the patient was admitted.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -1673,7 +1676,7 @@
     <t>The reason for re-admission of this hospitalization encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092|3.0.0</t>
   </si>
   <si>
     <t>PV1-13</t>
@@ -1697,7 +1700,7 @@
     <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-diet</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
@@ -1718,7 +1721,7 @@
     <t>Special courtesies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
   </si>
   <si>
     <t>.specialCourtesiesCode</t>
@@ -1739,7 +1742,7 @@
     <t>Special arrangements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
   </si>
   <si>
     <t>.specialArrangementCode</t>
@@ -1772,7 +1775,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition|2.2.0</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1808,7 +1811,7 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
 </t>
   </si>
   <si>
@@ -1861,7 +1864,7 @@
 There may be many levels in the hierachy, and this may only pic specific levels that are required for a specific usage scenario.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-physical-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-type|2.2.0</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -1891,7 +1894,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>
@@ -2222,17 +2225,17 @@
   <dimension ref="A1:AN107"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.8984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="53.8984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.734375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.4921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="46.4921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.61328125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="129.125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="120.5703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2241,26 +2244,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.8515625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.59765625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="68.296875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.47265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="99.8984375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="187.49609375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="86.17578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="161.73828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3455,7 +3458,7 @@
         <v>81</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>81</v>
@@ -3523,10 +3526,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3549,16 +3552,16 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3584,13 +3587,13 @@
         <v>81</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>81</v>
@@ -3608,7 +3611,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3637,10 +3640,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3663,16 +3666,16 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3698,13 +3701,13 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
@@ -3722,7 +3725,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3751,10 +3754,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3780,13 +3783,13 @@
         <v>131</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3836,7 +3839,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3865,10 +3868,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3891,16 +3894,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3926,13 +3929,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -3950,7 +3953,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3979,14 +3982,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4005,16 +4008,16 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4064,7 +4067,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4082,7 +4085,7 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>81</v>
@@ -4093,14 +4096,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4119,16 +4122,16 @@
         <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4178,7 +4181,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4196,7 +4199,7 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>81</v>
@@ -4207,10 +4210,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4236,10 +4239,10 @@
         <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4288,7 +4291,7 @@
         <v>116</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4317,13 +4320,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>81</v>
@@ -4345,13 +4348,13 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4402,7 +4405,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4411,7 +4414,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>118</v>
@@ -4431,10 +4434,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4460,16 +4463,16 @@
         <v>110</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4518,7 +4521,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4536,7 +4539,7 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>81</v>
@@ -4547,10 +4550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4573,13 +4576,13 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4630,7 +4633,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4645,24 +4648,24 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4771,10 +4774,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4885,10 +4888,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4911,19 +4914,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4948,13 +4951,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4972,7 +4975,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4990,21 +4993,21 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5027,19 +5030,19 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5064,11 +5067,11 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -5086,7 +5089,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5104,21 +5107,21 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5144,16 +5147,16 @@
         <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5166,7 +5169,7 @@
         <v>81</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>81</v>
@@ -5202,7 +5205,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5220,21 +5223,21 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5260,13 +5263,13 @@
         <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5280,7 +5283,7 @@
         <v>81</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>81</v>
@@ -5316,7 +5319,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5334,21 +5337,21 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5371,13 +5374,13 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5428,7 +5431,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5446,21 +5449,21 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5483,16 +5486,16 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5542,7 +5545,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5560,21 +5563,21 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5597,16 +5600,16 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5632,13 +5635,13 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5656,7 +5659,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>89</v>
@@ -5671,24 +5674,24 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5711,16 +5714,16 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5770,7 +5773,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5799,10 +5802,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5911,10 +5914,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6025,14 +6028,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6054,16 +6057,16 @@
         <v>110</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -6112,7 +6115,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6130,7 +6133,7 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -6141,10 +6144,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6167,13 +6170,13 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6200,13 +6203,13 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
@@ -6224,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>89</v>
@@ -6253,10 +6256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6279,13 +6282,13 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6336,7 +6339,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>89</v>
@@ -6365,10 +6368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6391,13 +6394,13 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6424,13 +6427,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6448,7 +6451,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>89</v>
@@ -6466,21 +6469,21 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6589,10 +6592,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6703,10 +6706,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6732,16 +6735,16 @@
         <v>131</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6790,7 +6793,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6808,21 +6811,21 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6848,13 +6851,13 @@
         <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6904,7 +6907,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6922,21 +6925,21 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6959,17 +6962,17 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -7018,7 +7021,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7036,21 +7039,21 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7076,14 +7079,14 @@
         <v>103</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7132,7 +7135,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7150,21 +7153,21 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7187,19 +7190,19 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7248,7 +7251,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7266,21 +7269,21 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7303,13 +7306,13 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7360,7 +7363,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7389,10 +7392,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7501,10 +7504,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7615,14 +7618,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7644,16 +7647,16 @@
         <v>110</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7702,7 +7705,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7720,7 +7723,7 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
@@ -7731,10 +7734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7757,13 +7760,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7790,13 +7793,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7814,7 +7817,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7843,10 +7846,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7869,13 +7872,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7926,7 +7929,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>89</v>
@@ -7955,10 +7958,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7969,7 +7972,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -7981,16 +7984,16 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8016,11 +8019,11 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8038,7 +8041,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8053,24 +8056,24 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8093,13 +8096,13 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8126,13 +8129,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8150,7 +8153,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8165,7 +8168,7 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>107</v>
@@ -8174,15 +8177,15 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8205,13 +8208,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8238,13 +8241,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8262,7 +8265,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8280,25 +8283,25 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8317,16 +8320,16 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8376,7 +8379,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8391,24 +8394,24 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8431,13 +8434,13 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8488,7 +8491,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8503,28 +8506,28 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8543,13 +8546,13 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8600,7 +8603,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8615,10 +8618,10 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
@@ -8629,10 +8632,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8655,13 +8658,13 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8712,7 +8715,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8727,24 +8730,24 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8853,10 +8856,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8967,14 +8970,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8996,16 +8999,16 @@
         <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9054,7 +9057,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9072,7 +9075,7 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
@@ -9083,10 +9086,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9109,16 +9112,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9144,13 +9147,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9168,7 +9171,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9183,24 +9186,24 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9223,13 +9226,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9280,7 +9283,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9298,21 +9301,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9335,13 +9338,13 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9392,7 +9395,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9407,24 +9410,24 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9447,13 +9450,13 @@
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9504,7 +9507,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9519,24 +9522,24 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9559,16 +9562,16 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9618,7 +9621,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9633,24 +9636,24 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9673,16 +9676,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9732,7 +9735,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9747,28 +9750,28 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9787,16 +9790,16 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9822,13 +9825,13 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -9846,7 +9849,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9861,28 +9864,28 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9901,16 +9904,16 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9960,7 +9963,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9975,24 +9978,24 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10015,13 +10018,13 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10072,7 +10075,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10090,7 +10093,7 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
@@ -10101,10 +10104,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10213,10 +10216,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10327,14 +10330,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10356,16 +10359,16 @@
         <v>110</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10414,7 +10417,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10432,7 +10435,7 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
@@ -10443,14 +10446,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10469,16 +10472,16 @@
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10528,7 +10531,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>89</v>
@@ -10543,24 +10546,24 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10583,13 +10586,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10616,13 +10619,13 @@
         <v>81</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
@@ -10640,7 +10643,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10669,10 +10672,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10695,13 +10698,13 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10752,7 +10755,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10770,7 +10773,7 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
@@ -10781,10 +10784,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10807,16 +10810,16 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10866,7 +10869,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10884,7 +10887,7 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
@@ -10895,10 +10898,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10921,16 +10924,16 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10980,7 +10983,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10998,7 +11001,7 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
@@ -11009,10 +11012,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11121,10 +11124,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11235,14 +11238,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11264,16 +11267,16 @@
         <v>110</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -11322,7 +11325,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11340,7 +11343,7 @@
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>81</v>
@@ -11351,10 +11354,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11377,13 +11380,13 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11434,7 +11437,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11452,21 +11455,21 @@
         <v>81</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11575,10 +11578,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11689,10 +11692,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11715,19 +11718,19 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -11752,13 +11755,13 @@
         <v>81</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -11776,7 +11779,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11794,21 +11797,21 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11831,19 +11834,19 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -11868,11 +11871,11 @@
         <v>81</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>81</v>
@@ -11890,7 +11893,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11908,21 +11911,21 @@
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11948,29 +11951,29 @@
         <v>131</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>81</v>
@@ -12006,7 +12009,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12024,21 +12027,21 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12064,13 +12067,13 @@
         <v>103</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12084,7 +12087,7 @@
         <v>81</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>81</v>
@@ -12120,7 +12123,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12138,21 +12141,21 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12175,13 +12178,13 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12232,7 +12235,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12250,21 +12253,21 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12287,16 +12290,16 @@
         <v>90</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12346,7 +12349,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12364,21 +12367,21 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12401,13 +12404,13 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12458,7 +12461,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12476,7 +12479,7 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
@@ -12487,10 +12490,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12513,13 +12516,13 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12546,13 +12549,13 @@
         <v>81</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -12570,7 +12573,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12588,21 +12591,21 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12625,13 +12628,13 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12658,13 +12661,13 @@
         <v>81</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>81</v>
@@ -12682,7 +12685,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12706,15 +12709,15 @@
         <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12737,19 +12740,19 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -12774,13 +12777,13 @@
         <v>81</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>81</v>
@@ -12798,7 +12801,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12816,21 +12819,21 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12853,13 +12856,13 @@
         <v>81</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12886,13 +12889,13 @@
         <v>81</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>81</v>
@@ -12910,7 +12913,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12928,21 +12931,21 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12965,13 +12968,13 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12998,13 +13001,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -13022,7 +13025,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13040,21 +13043,21 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13077,13 +13080,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13134,7 +13137,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13152,21 +13155,21 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13189,13 +13192,13 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13222,11 +13225,11 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -13244,7 +13247,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13262,21 +13265,21 @@
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13299,16 +13302,16 @@
         <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13358,7 +13361,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13376,7 +13379,7 @@
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
@@ -13387,10 +13390,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13499,10 +13502,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13613,14 +13616,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -13642,16 +13645,16 @@
         <v>110</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
@@ -13700,7 +13703,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13718,7 +13721,7 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
@@ -13729,10 +13732,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13755,13 +13758,13 @@
         <v>81</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13812,7 +13815,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>89</v>
@@ -13827,24 +13830,24 @@
         <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13867,16 +13870,16 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13902,13 +13905,13 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -13926,7 +13929,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -13944,7 +13947,7 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
@@ -13955,10 +13958,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13981,16 +13984,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14016,11 +14019,11 @@
         <v>81</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
@@ -14038,7 +14041,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14067,10 +14070,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14093,13 +14096,13 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14150,7 +14153,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14168,7 +14171,7 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>
@@ -14179,10 +14182,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14205,13 +14208,13 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14262,7 +14265,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14277,24 +14280,24 @@
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14317,16 +14320,16 @@
         <v>81</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14376,7 +14379,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14391,10 +14394,10 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>81</v>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-encounter.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="613">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Encounter|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Encounter</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -428,7 +428,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -441,14 +441,14 @@
     <t>Encounter.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -470,9 +470,6 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0</t>
-  </si>
-  <si>
     <t>Encounter.meta.security</t>
   </si>
   <si>
@@ -495,7 +492,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -519,7 +516,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -562,7 +559,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -638,7 +635,7 @@
     <t>estimatedDischargeDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date}
 </t>
   </si>
   <si>
@@ -748,7 +745,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -834,7 +831,7 @@
     <t>Encounter.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -949,7 +946,7 @@
     <t>Classification of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -1130,7 +1127,7 @@
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1154,7 +1151,7 @@
     <t>Broad categorization of the service that is to be provided.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type</t>
   </si>
   <si>
     <t>PV1-10</t>
@@ -1169,7 +1166,7 @@
     <t>Indicates the urgency of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
   </si>
   <si>
     <t>.priorityCode</t>
@@ -1188,7 +1185,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|Group|4.0.1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1216,7 +1213,7 @@
     <t>Encounter.episodeOfCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(EpisodeOfCare|4.0.1)
+    <t xml:space="preserve">Reference(EpisodeOfCare)
 </t>
   </si>
   <si>
@@ -1242,7 +1239,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(ServiceRequest)
 </t>
   </si>
   <si>
@@ -1297,7 +1294,7 @@
     <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1327,7 +1324,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole)
 </t>
   </si>
   <si>
@@ -1352,7 +1349,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment)
 </t>
   </si>
   <si>
@@ -1433,7 +1430,7 @@
     <t>Reason why the encounter takes place.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1451,7 +1448,7 @@
     <t>Encounter.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1|Observation|4.0.1|ImmunizationRecommendation|4.0.1)
+    <t xml:space="preserve">Reference(Condition|Procedure|Observation|ImmunizationRecommendation)
 </t>
   </si>
   <si>
@@ -1486,7 +1483,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1)
+    <t xml:space="preserve">Reference(Condition|Procedure)
 </t>
   </si>
   <si>
@@ -1517,7 +1514,7 @@
     <t>The type of diagnosis this condition represents.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnosis-role</t>
   </si>
   <si>
     <t>Encounter.diagnosis.rank</t>
@@ -1539,7 +1536,7 @@
     <t>Encounter.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Account|4.0.1)
+    <t xml:space="preserve">Reference(Account)
 </t>
   </si>
   <si>
@@ -1630,7 +1627,7 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -1655,7 +1652,7 @@
     <t>From where the patient was admitted.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -1676,7 +1673,7 @@
     <t>The reason for re-admission of this hospitalization encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
   </si>
   <si>
     <t>PV1-13</t>
@@ -1700,7 +1697,7 @@
     <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diet</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
@@ -1721,7 +1718,7 @@
     <t>Special courtesies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy</t>
   </si>
   <si>
     <t>.specialCourtesiesCode</t>
@@ -1742,7 +1739,7 @@
     <t>Special arrangements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements</t>
   </si>
   <si>
     <t>.specialArrangementCode</t>
@@ -1775,7 +1772,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1811,7 +1808,7 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location)
 </t>
   </si>
   <si>
@@ -1864,7 +1861,7 @@
 There may be many levels in the hierachy, and this may only pic specific levels that are required for a specific usage scenario.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-type|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-physical-type</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -1894,7 +1891,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
 </t>
   </si>
   <si>
@@ -2225,17 +2222,17 @@
   <dimension ref="A1:AN107"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.4921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.4921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.61328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="53.8984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="53.8984375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="22.734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="120.5703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="129.125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2244,26 +2241,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="68.296875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.47265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="73.8515625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="44.59765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="86.17578125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="28.5078125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="161.73828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="99.8984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="187.49609375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3458,7 +3455,7 @@
         <v>81</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>81</v>
@@ -3526,10 +3523,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3552,16 +3549,16 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3587,31 +3584,31 @@
         <v>81</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y12" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Z12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3640,10 +3637,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3666,16 +3663,16 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3701,31 +3698,31 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="Z13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3754,10 +3751,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3783,13 +3780,13 @@
         <v>131</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3839,7 +3836,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3868,10 +3865,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3894,16 +3891,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3929,31 +3926,31 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3982,14 +3979,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4008,16 +4005,16 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4067,7 +4064,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4085,7 +4082,7 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>81</v>
@@ -4096,14 +4093,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4122,16 +4119,16 @@
         <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4181,7 +4178,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4199,7 +4196,7 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>81</v>
@@ -4210,10 +4207,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4239,10 +4236,10 @@
         <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4291,7 +4288,7 @@
         <v>116</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4320,13 +4317,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>81</v>
@@ -4348,13 +4345,13 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4405,7 +4402,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4414,7 +4411,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>118</v>
@@ -4434,10 +4431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4463,16 +4460,16 @@
         <v>110</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4521,7 +4518,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4539,7 +4536,7 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>81</v>
@@ -4550,10 +4547,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4576,13 +4573,13 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4633,7 +4630,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4648,24 +4645,24 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>216</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4774,10 +4771,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4888,10 +4885,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4914,19 +4911,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4951,31 +4948,31 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z24" t="s" s="2">
+      <c r="AA24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4993,21 +4990,21 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5030,19 +5027,19 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5067,29 +5064,29 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5107,21 +5104,21 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5147,16 +5144,16 @@
         <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5169,43 +5166,43 @@
         <v>81</v>
       </c>
       <c r="T26" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5223,21 +5220,21 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>246</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5263,13 +5260,13 @@
         <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5283,43 +5280,43 @@
         <v>81</v>
       </c>
       <c r="T27" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5337,21 +5334,21 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5374,13 +5371,13 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5431,7 +5428,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5449,21 +5446,21 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5486,16 +5483,16 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5545,7 +5542,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5563,21 +5560,21 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>269</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5600,16 +5597,16 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5635,14 +5632,14 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="Z30" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5659,7 +5656,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>89</v>
@@ -5674,24 +5671,24 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>279</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5714,16 +5711,16 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5773,7 +5770,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5802,10 +5799,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5914,10 +5911,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6028,14 +6025,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6057,16 +6054,16 @@
         <v>110</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -6115,7 +6112,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6133,7 +6130,7 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -6144,10 +6141,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6170,13 +6167,13 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6203,14 +6200,14 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6227,7 +6224,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>89</v>
@@ -6256,10 +6253,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6282,13 +6279,13 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6339,7 +6336,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>89</v>
@@ -6368,10 +6365,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6394,13 +6391,13 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6427,14 +6424,14 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>300</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6451,7 +6448,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>89</v>
@@ -6469,21 +6466,21 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>303</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6592,10 +6589,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6706,10 +6703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6735,16 +6732,16 @@
         <v>131</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6793,7 +6790,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6811,21 +6808,21 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6851,13 +6848,13 @@
         <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6907,7 +6904,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6925,21 +6922,21 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>320</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6962,17 +6959,17 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -7021,7 +7018,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7039,21 +7036,21 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>327</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7079,14 +7076,14 @@
         <v>103</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7135,7 +7132,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7153,21 +7150,21 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7190,19 +7187,19 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7251,7 +7248,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7269,21 +7266,21 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>343</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7306,13 +7303,13 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7363,7 +7360,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7392,10 +7389,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7504,10 +7501,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7618,14 +7615,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7647,16 +7644,16 @@
         <v>110</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7705,7 +7702,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7723,7 +7720,7 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
@@ -7734,10 +7731,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7760,13 +7757,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7793,14 +7790,14 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>300</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7817,7 +7814,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7846,10 +7843,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7872,13 +7869,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7929,7 +7926,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>89</v>
@@ -7958,10 +7955,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7972,7 +7969,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -7984,16 +7981,16 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8019,11 +8016,11 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8041,7 +8038,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8056,24 +8053,24 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>363</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8096,13 +8093,13 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8129,14 +8126,14 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
       </c>
@@ -8153,7 +8150,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8168,7 +8165,7 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>107</v>
@@ -8177,15 +8174,15 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8208,13 +8205,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8241,14 +8238,14 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8265,7 +8262,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8283,25 +8280,25 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>376</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8320,16 +8317,16 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8379,7 +8376,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8394,24 +8391,24 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AM54" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>386</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8434,13 +8431,13 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8491,7 +8488,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8506,28 +8503,28 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>393</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8546,13 +8543,13 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8603,7 +8600,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8618,10 +8615,10 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
@@ -8632,10 +8629,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8658,13 +8655,13 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8715,7 +8712,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8730,24 +8727,24 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>406</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8856,10 +8853,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8970,14 +8967,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8999,16 +8996,16 @@
         <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9057,7 +9054,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9075,7 +9072,7 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
@@ -9086,10 +9083,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9112,16 +9109,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9147,13 +9144,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9171,7 +9168,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9186,24 +9183,24 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>417</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9226,13 +9223,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9283,7 +9280,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9301,21 +9298,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>422</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9338,13 +9335,13 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9395,7 +9392,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9410,24 +9407,24 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>430</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9450,13 +9447,13 @@
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9507,7 +9504,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9522,24 +9519,24 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>436</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9562,16 +9559,16 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9621,7 +9618,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9636,24 +9633,24 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AM65" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>444</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9676,16 +9673,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9735,7 +9732,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9750,28 +9747,28 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9790,16 +9787,16 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9825,14 +9822,14 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>458</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
       </c>
@@ -9849,7 +9846,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9864,28 +9861,28 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AL67" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AL67" t="s" s="2">
+      <c r="AM67" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>462</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9904,16 +9901,16 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="L68" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="M68" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9963,7 +9960,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9978,24 +9975,24 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="AM68" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>462</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10018,13 +10015,13 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10075,7 +10072,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10093,7 +10090,7 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
@@ -10104,10 +10101,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10216,10 +10213,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10330,14 +10327,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10359,16 +10356,16 @@
         <v>110</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10417,7 +10414,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10435,7 +10432,7 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
@@ -10446,14 +10443,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10472,16 +10469,16 @@
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M73" t="s" s="2">
-        <v>477</v>
-      </c>
       <c r="N73" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10531,7 +10528,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>89</v>
@@ -10546,24 +10543,24 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="AL73" t="s" s="2">
+      <c r="AM73" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>480</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10586,13 +10583,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10619,14 +10616,14 @@
         <v>81</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
       </c>
@@ -10643,7 +10640,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10672,10 +10669,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10698,13 +10695,13 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10755,7 +10752,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10773,7 +10770,7 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
@@ -10784,10 +10781,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10810,16 +10807,16 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10869,7 +10866,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10887,7 +10884,7 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
@@ -10898,10 +10895,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10924,16 +10921,16 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10983,7 +10980,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11001,7 +10998,7 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
@@ -11012,10 +11009,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11124,10 +11121,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11238,14 +11235,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11267,16 +11264,16 @@
         <v>110</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -11325,7 +11322,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11343,7 +11340,7 @@
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>81</v>
@@ -11354,10 +11351,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11380,13 +11377,13 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11437,7 +11434,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11455,21 +11452,21 @@
         <v>81</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11578,10 +11575,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11692,10 +11689,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11718,19 +11715,19 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -11755,31 +11752,31 @@
         <v>81</v>
       </c>
       <c r="X84" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Y84" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Y84" t="s" s="2">
+      <c r="Z84" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z84" t="s" s="2">
+      <c r="AA84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11797,21 +11794,21 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11834,19 +11831,19 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L85" t="s" s="2">
-        <v>231</v>
-      </c>
       <c r="M85" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="N85" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="O85" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -11871,29 +11868,29 @@
         <v>81</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11911,21 +11908,21 @@
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11951,65 +11948,65 @@
         <v>131</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N86" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="O86" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T86" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12027,21 +12024,21 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>246</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12067,13 +12064,13 @@
         <v>103</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12087,43 +12084,43 @@
         <v>81</v>
       </c>
       <c r="T87" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12141,21 +12138,21 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12178,13 +12175,13 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12235,7 +12232,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12253,21 +12250,21 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12290,16 +12287,16 @@
         <v>90</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12349,7 +12346,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12367,21 +12364,21 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>269</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12404,13 +12401,13 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="M90" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12461,7 +12458,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12479,7 +12476,7 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
@@ -12490,10 +12487,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12516,13 +12513,13 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12549,14 +12546,14 @@
         <v>81</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="Z91" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="Z91" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
       </c>
@@ -12573,7 +12570,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12591,21 +12588,21 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>531</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12628,13 +12625,13 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12661,14 +12658,14 @@
         <v>81</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>536</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>81</v>
       </c>
@@ -12685,7 +12682,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12709,15 +12706,15 @@
         <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12740,19 +12737,19 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -12777,14 +12774,14 @@
         <v>81</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="Z93" t="s" s="2">
-        <v>544</v>
-      </c>
       <c r="AA93" t="s" s="2">
         <v>81</v>
       </c>
@@ -12801,7 +12798,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12819,21 +12816,21 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>546</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12856,13 +12853,13 @@
         <v>81</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12889,14 +12886,14 @@
         <v>81</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>551</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>81</v>
       </c>
@@ -12913,7 +12910,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12931,21 +12928,21 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>553</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12968,13 +12965,13 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13001,14 +12998,14 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="Z95" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>558</v>
-      </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
       </c>
@@ -13025,7 +13022,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13043,21 +13040,21 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>560</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13080,13 +13077,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13137,7 +13134,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13155,21 +13152,21 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>565</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13192,13 +13189,13 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13225,11 +13222,11 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -13247,7 +13244,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13265,21 +13262,21 @@
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>571</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13302,16 +13299,16 @@
         <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13361,7 +13358,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13379,7 +13376,7 @@
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
@@ -13390,10 +13387,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13502,10 +13499,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13616,14 +13613,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -13645,16 +13642,16 @@
         <v>110</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
@@ -13703,7 +13700,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13721,7 +13718,7 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
@@ -13732,10 +13729,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13758,13 +13755,13 @@
         <v>81</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13815,7 +13812,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>89</v>
@@ -13830,24 +13827,24 @@
         <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AM102" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="AL102" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AM102" t="s" s="2">
+      <c r="AN102" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>586</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13870,16 +13867,16 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13905,14 +13902,14 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Y103" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z103" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="Z103" t="s" s="2">
-        <v>592</v>
-      </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
       </c>
@@ -13929,7 +13926,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -13947,7 +13944,7 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
@@ -13958,10 +13955,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13984,16 +13981,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14019,11 +14016,11 @@
         <v>81</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
@@ -14041,7 +14038,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14070,10 +14067,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14096,13 +14093,13 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14153,7 +14150,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14171,7 +14168,7 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>
@@ -14182,10 +14179,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14208,13 +14205,13 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14265,7 +14262,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14280,24 +14277,24 @@
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AL106" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>606</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14320,16 +14317,16 @@
         <v>81</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14379,7 +14376,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14394,10 +14391,10 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AL107" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>81</v>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-encounter.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="614">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Encounter</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Encounter|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -428,7 +428,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -441,14 +441,14 @@
     <t>Encounter.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -470,6 +470,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0</t>
+  </si>
+  <si>
     <t>Encounter.meta.security</t>
   </si>
   <si>
@@ -492,7 +495,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -516,7 +519,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -559,7 +562,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -635,7 +638,7 @@
     <t>estimatedDischargeDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date|2.2.0}
 </t>
   </si>
   <si>
@@ -745,7 +748,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type|2.2.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -831,7 +834,7 @@
     <t>Encounter.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -946,7 +949,7 @@
     <t>Classification of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -1127,7 +1130,7 @@
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type|2.2.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1151,7 +1154,7 @@
     <t>Broad categorization of the service that is to be provided.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>PV1-10</t>
@@ -1166,7 +1169,7 @@
     <t>Indicates the urgency of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority|3.0.0</t>
   </si>
   <si>
     <t>.priorityCode</t>
@@ -1185,7 +1188,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1213,7 +1216,7 @@
     <t>Encounter.episodeOfCare</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(EpisodeOfCare)
+    <t xml:space="preserve">Reference(EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1239,7 +1242,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1294,7 +1297,7 @@
     <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1324,7 +1327,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1349,7 +1352,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.2.0)
 </t>
   </si>
   <si>
@@ -1430,7 +1433,7 @@
     <t>Reason why the encounter takes place.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1448,7 +1451,7 @@
     <t>Encounter.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure|Observation|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1|Observation|4.0.1|ImmunizationRecommendation|4.0.1)
 </t>
   </si>
   <si>
@@ -1483,7 +1486,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -1514,7 +1517,7 @@
     <t>The type of diagnosis this condition represents.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnosis-role</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.0.1</t>
   </si>
   <si>
     <t>Encounter.diagnosis.rank</t>
@@ -1536,7 +1539,7 @@
     <t>Encounter.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Account)
+    <t xml:space="preserve">Reference(Account|4.0.1)
 </t>
   </si>
   <si>
@@ -1627,7 +1630,7 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1652,7 +1655,7 @@
     <t>From where the patient was admitted.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -1673,7 +1676,7 @@
     <t>The reason for re-admission of this hospitalization encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092|3.0.0</t>
   </si>
   <si>
     <t>PV1-13</t>
@@ -1697,7 +1700,7 @@
     <t>Medical, cultural or ethical food preferences to help with catering requirements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-diet</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diet|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=EVN, code="diet"]</t>
@@ -1718,7 +1721,7 @@
     <t>Special courtesies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-courtesy|4.0.1</t>
   </si>
   <si>
     <t>.specialCourtesiesCode</t>
@@ -1739,7 +1742,7 @@
     <t>Special arrangements.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-special-arrangements|4.0.1</t>
   </si>
   <si>
     <t>.specialArrangementCode</t>
@@ -1772,7 +1775,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition|2.2.0</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1808,7 +1811,7 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
 </t>
   </si>
   <si>
@@ -1861,7 +1864,7 @@
 There may be many levels in the hierachy, and this may only pic specific levels that are required for a specific usage scenario.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-physical-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-type|2.2.0</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -1891,7 +1894,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>
@@ -2222,17 +2225,17 @@
   <dimension ref="A1:AN107"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.8984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="53.8984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.734375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.4921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="46.4921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.61328125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="129.125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="120.5703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2241,26 +2244,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.1875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.8515625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.59765625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="68.296875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.47265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="99.8984375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="187.49609375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="86.17578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="161.73828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3455,7 +3458,7 @@
         <v>81</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>81</v>
@@ -3523,10 +3526,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3549,16 +3552,16 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3584,13 +3587,13 @@
         <v>81</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>81</v>
@@ -3608,7 +3611,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3637,10 +3640,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3663,16 +3666,16 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3698,13 +3701,13 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
@@ -3722,7 +3725,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3751,10 +3754,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3780,13 +3783,13 @@
         <v>131</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3836,7 +3839,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3865,10 +3868,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3891,16 +3894,16 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3926,13 +3929,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -3950,7 +3953,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3979,14 +3982,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4005,16 +4008,16 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4064,7 +4067,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4082,7 +4085,7 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>81</v>
@@ -4093,14 +4096,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4119,16 +4122,16 @@
         <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4178,7 +4181,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4196,7 +4199,7 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>81</v>
@@ -4207,10 +4210,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4236,10 +4239,10 @@
         <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4288,7 +4291,7 @@
         <v>116</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4317,13 +4320,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>81</v>
@@ -4345,13 +4348,13 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4402,7 +4405,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4411,7 +4414,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>118</v>
@@ -4431,10 +4434,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4460,16 +4463,16 @@
         <v>110</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4518,7 +4521,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4536,7 +4539,7 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>81</v>
@@ -4547,10 +4550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4573,13 +4576,13 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4630,7 +4633,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4645,24 +4648,24 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4771,10 +4774,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4885,10 +4888,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4911,19 +4914,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4948,13 +4951,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4972,7 +4975,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4990,21 +4993,21 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5027,19 +5030,19 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5064,11 +5067,11 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -5086,7 +5089,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5104,21 +5107,21 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5144,16 +5147,16 @@
         <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5166,7 +5169,7 @@
         <v>81</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>81</v>
@@ -5202,7 +5205,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5220,21 +5223,21 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5260,13 +5263,13 @@
         <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5280,7 +5283,7 @@
         <v>81</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>81</v>
@@ -5316,7 +5319,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5334,21 +5337,21 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5371,13 +5374,13 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5428,7 +5431,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5446,21 +5449,21 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5483,16 +5486,16 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5542,7 +5545,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5560,21 +5563,21 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5597,16 +5600,16 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5632,13 +5635,13 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5656,7 +5659,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>89</v>
@@ -5671,24 +5674,24 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5711,16 +5714,16 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5770,7 +5773,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5799,10 +5802,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5911,10 +5914,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6025,14 +6028,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6054,16 +6057,16 @@
         <v>110</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -6112,7 +6115,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6130,7 +6133,7 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -6141,10 +6144,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6167,13 +6170,13 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6200,13 +6203,13 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
@@ -6224,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>89</v>
@@ -6253,10 +6256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6279,13 +6282,13 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6336,7 +6339,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>89</v>
@@ -6365,10 +6368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6391,13 +6394,13 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6424,13 +6427,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6448,7 +6451,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>89</v>
@@ -6466,21 +6469,21 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6589,10 +6592,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6703,10 +6706,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6732,16 +6735,16 @@
         <v>131</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6790,7 +6793,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6808,21 +6811,21 @@
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6848,13 +6851,13 @@
         <v>103</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6904,7 +6907,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6922,21 +6925,21 @@
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6959,17 +6962,17 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -7018,7 +7021,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7036,21 +7039,21 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7076,14 +7079,14 @@
         <v>103</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7132,7 +7135,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7150,21 +7153,21 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7187,19 +7190,19 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7248,7 +7251,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7266,21 +7269,21 @@
         <v>81</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7303,13 +7306,13 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7360,7 +7363,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7389,10 +7392,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7501,10 +7504,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7615,14 +7618,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7644,16 +7647,16 @@
         <v>110</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7702,7 +7705,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7720,7 +7723,7 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
@@ -7731,10 +7734,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7757,13 +7760,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7790,13 +7793,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7814,7 +7817,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7843,10 +7846,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7869,13 +7872,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7926,7 +7929,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>89</v>
@@ -7955,10 +7958,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7969,7 +7972,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -7981,16 +7984,16 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8016,11 +8019,11 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8038,7 +8041,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8053,24 +8056,24 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8093,13 +8096,13 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8126,13 +8129,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8150,7 +8153,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8165,7 +8168,7 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>107</v>
@@ -8174,15 +8177,15 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8205,13 +8208,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8238,13 +8241,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8262,7 +8265,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8280,25 +8283,25 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8317,16 +8320,16 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8376,7 +8379,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8391,24 +8394,24 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8431,13 +8434,13 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8488,7 +8491,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8503,28 +8506,28 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8543,13 +8546,13 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8600,7 +8603,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8615,10 +8618,10 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
@@ -8629,10 +8632,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8655,13 +8658,13 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8712,7 +8715,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8727,24 +8730,24 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8853,10 +8856,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8967,14 +8970,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8996,16 +8999,16 @@
         <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9054,7 +9057,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9072,7 +9075,7 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
@@ -9083,10 +9086,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9109,16 +9112,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9144,13 +9147,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9168,7 +9171,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9183,24 +9186,24 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9223,13 +9226,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9280,7 +9283,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9298,21 +9301,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9335,13 +9338,13 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9392,7 +9395,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9407,24 +9410,24 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9447,13 +9450,13 @@
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9504,7 +9507,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9519,24 +9522,24 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9559,16 +9562,16 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9618,7 +9621,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9633,24 +9636,24 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9673,16 +9676,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9732,7 +9735,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9747,28 +9750,28 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9787,16 +9790,16 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9822,13 +9825,13 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -9846,7 +9849,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9861,28 +9864,28 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9901,16 +9904,16 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9960,7 +9963,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9975,24 +9978,24 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10015,13 +10018,13 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10072,7 +10075,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10090,7 +10093,7 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
@@ -10101,10 +10104,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10213,10 +10216,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10327,14 +10330,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10356,16 +10359,16 @@
         <v>110</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10414,7 +10417,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10432,7 +10435,7 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
@@ -10443,14 +10446,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10469,16 +10472,16 @@
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10528,7 +10531,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>89</v>
@@ -10543,24 +10546,24 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10583,13 +10586,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10616,13 +10619,13 @@
         <v>81</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
@@ -10640,7 +10643,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10669,10 +10672,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10695,13 +10698,13 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10752,7 +10755,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10770,7 +10773,7 @@
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
@@ -10781,10 +10784,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10807,16 +10810,16 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10866,7 +10869,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10884,7 +10887,7 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
@@ -10895,10 +10898,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10921,16 +10924,16 @@
         <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10980,7 +10983,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10998,7 +11001,7 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
@@ -11009,10 +11012,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11121,10 +11124,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11235,14 +11238,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11264,16 +11267,16 @@
         <v>110</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -11322,7 +11325,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11340,7 +11343,7 @@
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>81</v>
@@ -11351,10 +11354,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11377,13 +11380,13 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11434,7 +11437,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11452,21 +11455,21 @@
         <v>81</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11575,10 +11578,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11689,10 +11692,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11715,19 +11718,19 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -11752,13 +11755,13 @@
         <v>81</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -11776,7 +11779,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11794,21 +11797,21 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11831,19 +11834,19 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -11868,11 +11871,11 @@
         <v>81</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>81</v>
@@ -11890,7 +11893,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11908,21 +11911,21 @@
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11948,29 +11951,29 @@
         <v>131</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>81</v>
@@ -12006,7 +12009,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12024,21 +12027,21 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12064,13 +12067,13 @@
         <v>103</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12084,7 +12087,7 @@
         <v>81</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>81</v>
@@ -12120,7 +12123,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12138,21 +12141,21 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12175,13 +12178,13 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12232,7 +12235,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12250,21 +12253,21 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12287,16 +12290,16 @@
         <v>90</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12346,7 +12349,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12364,21 +12367,21 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12401,13 +12404,13 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12458,7 +12461,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12476,7 +12479,7 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
@@ -12487,10 +12490,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12513,13 +12516,13 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12546,13 +12549,13 @@
         <v>81</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -12570,7 +12573,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12588,21 +12591,21 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12625,13 +12628,13 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12658,13 +12661,13 @@
         <v>81</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>81</v>
@@ -12682,7 +12685,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12706,15 +12709,15 @@
         <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12737,19 +12740,19 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -12774,13 +12777,13 @@
         <v>81</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>81</v>
@@ -12798,7 +12801,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12816,21 +12819,21 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12853,13 +12856,13 @@
         <v>81</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12886,13 +12889,13 @@
         <v>81</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>81</v>
@@ -12910,7 +12913,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12928,21 +12931,21 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12965,13 +12968,13 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12998,13 +13001,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -13022,7 +13025,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13040,21 +13043,21 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13077,13 +13080,13 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13134,7 +13137,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13152,21 +13155,21 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13189,13 +13192,13 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13222,11 +13225,11 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -13244,7 +13247,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13262,21 +13265,21 @@
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13299,16 +13302,16 @@
         <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13358,7 +13361,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13376,7 +13379,7 @@
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
@@ -13387,10 +13390,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13499,10 +13502,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13613,14 +13616,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -13642,16 +13645,16 @@
         <v>110</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
@@ -13700,7 +13703,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13718,7 +13721,7 @@
         <v>81</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
@@ -13729,10 +13732,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13755,13 +13758,13 @@
         <v>81</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13812,7 +13815,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>89</v>
@@ -13827,24 +13830,24 @@
         <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13867,16 +13870,16 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13902,13 +13905,13 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -13926,7 +13929,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -13944,7 +13947,7 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
@@ -13955,10 +13958,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13981,16 +13984,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14016,11 +14019,11 @@
         <v>81</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
@@ -14038,7 +14041,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14067,10 +14070,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14093,13 +14096,13 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14150,7 +14153,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14168,7 +14171,7 @@
         <v>81</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>
@@ -14179,10 +14182,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14205,13 +14208,13 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14262,7 +14265,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14277,24 +14280,24 @@
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14317,16 +14320,16 @@
         <v>81</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14376,7 +14379,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14391,10 +14394,10 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>81</v>
